--- a/artfynd/A 5398-2026 artfynd.xlsx
+++ b/artfynd/A 5398-2026 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>80815268</v>
+        <v>95556123</v>
       </c>
       <c r="B2" t="n">
-        <v>95717</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,27 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220686</v>
+        <v>1339</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>328716.5720502932</v>
+        <v>328717</v>
       </c>
       <c r="R2" t="n">
-        <v>6400627.624587517</v>
+        <v>6400628</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -749,22 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-11-07</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-11-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,7 +768,27 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Granskog; inslag av björk</t>
+          <t>Lite äldre skog, men inget särskilt; produktionsskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -802,15 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>95556123</v>
+        <v>80815268</v>
       </c>
       <c r="B3" t="n">
-        <v>90005</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98194</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -818,26 +817,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1339</v>
+        <v>220686</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -845,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>328716.5720502932</v>
+        <v>328717</v>
       </c>
       <c r="R3" t="n">
-        <v>6400627.624587517</v>
+        <v>6400628</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -875,22 +875,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-08-17</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-11-07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-08-17</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-11-07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,27 +900,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Lite äldre skog, men inget särskilt; produktionsskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Granskog; inslag av björk</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>

--- a/artfynd/A 5398-2026 artfynd.xlsx
+++ b/artfynd/A 5398-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -803,6 +808,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95556123</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -915,8 +925,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80815268</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>